--- a/scripts/datos-prueba/usuarios-prueba.xlsx
+++ b/scripts/datos-prueba/usuarios-prueba.xlsx
@@ -234,6 +234,11 @@
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
         <t>P. ej. «Liberación para pago» o «Todos».</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Opcional. Si se llena, la persona solo recibe copia de los trámites dirigidos a esa subsecretaría (p. ej. quien apoya al subsecretario a firmar). Vacía = todos los trámites.</t>
       </text>
     </comment>
   </commentList>
@@ -579,7 +584,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2. Hoja «Solo copia»: personas o áreas que solo reciben correos y no entran a la aplicación (p. ej. Tesorería).</t>
+          <t>2. Hoja «Solo copia»: personas o áreas que solo reciben correos y no entran a la aplicación (p. ej. Tesorería). Columna «Subsecretaría» (opcional): si se llena, la persona solo recibe copia de los trámites de esa subsecretaría.</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1223,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1242,6 +1248,11 @@
           <t>Qué correos debe recibir</t>
         </is>
       </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Subsecretaría</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -1259,6 +1270,7 @@
           <t>Liberación para pago</t>
         </is>
       </c>
+      <c r="D2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -1276,151 +1288,229 @@
           <t>Liberación para pago</t>
         </is>
       </c>
+      <c r="D3" s="6" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="n"/>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>asistente.gestion@prueba.gov.co</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Asistente Gestión Institucional</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>aprobación del WF y lote nivel 1, rechazos, reinicios y anulaciones</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Gestión Institucional</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="n"/>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>asistente.calidad@prueba.gov.co</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Asistente Calidad y Pertinencia</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>aprobación del WF y lote nivel 1, rechazos, reinicios y anulaciones</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Calidad y Pertinencia</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="n"/>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>asistente.acceso@prueba.gov.co</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Asistente Acceso y Permanencia</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>aprobación del WF y lote nivel 1, rechazos, reinicios y anulaciones</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Acceso y Permanencia</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n"/>
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n"/>
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
       <c r="B10" s="6" t="n"/>
       <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n"/>
       <c r="B11" s="6" t="n"/>
       <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n"/>
       <c r="B12" s="6" t="n"/>
       <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
       <c r="B15" s="6" t="n"/>
       <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
       <c r="B17" s="6" t="n"/>
       <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
       <c r="B18" s="6" t="n"/>
       <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
       <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
       <c r="B23" s="6" t="n"/>
       <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
       <c r="B24" s="6" t="n"/>
       <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
       <c r="B25" s="6" t="n"/>
       <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
       <c r="B26" s="6" t="n"/>
       <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
       <c r="B27" s="6" t="n"/>
       <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
       <c r="B28" s="6" t="n"/>
       <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
       <c r="B29" s="6" t="n"/>
       <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
       <c r="B30" s="6" t="n"/>
       <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
       <c r="B31" s="6" t="n"/>
       <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
       <c r="B32" s="6" t="n"/>
       <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
